--- a/output/pdf_financials_xlsx/EPRX.xlsx
+++ b/output/pdf_financials_xlsx/EPRX.xlsx
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6.428293</v>
+        <v>17.909596</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.902991</v>
+        <v>17.617452</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>20.363124</v>
+        <v>27.847229</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>16.079276</v>
+        <v>27.003411</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>21.331656</v>
+        <v>38.434039</v>
       </c>
     </row>
     <row r="11">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-6.428293</v>
+        <v>-17.909596</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.902991</v>
+        <v>-17.617452</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-20.363124</v>
+        <v>-27.847229</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-16.079276</v>
+        <v>-27.003411</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-21.331656</v>
+        <v>-38.434039</v>
       </c>
     </row>
     <row r="12">
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.06572799999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.431799</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.862969</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>1.159943</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1.412516</v>
       </c>
     </row>
     <row r="13">
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-24.337889</v>
+        <v>-24.403617</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-18.990764</v>
+        <v>-19.422563</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-28.966006</v>
+        <v>-29.828975</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-25.744489</v>
+        <v>-26.904432</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-38.605652</v>
+        <v>-40.018168</v>
       </c>
     </row>
     <row r="28">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-24.337889</v>
+        <v>-24.403617</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-18.84287</v>
+        <v>-19.274669</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-28.810479</v>
+        <v>-29.673448</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-25.57277</v>
+        <v>-26.732713</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-38.367935</v>
+        <v>-39.780451</v>
       </c>
     </row>
     <row r="30">
@@ -1205,10 +1205,10 @@
         <v>19.341756</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>33.101294</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>80.56348199999999</v>
       </c>
     </row>
     <row r="35">
@@ -1249,10 +1249,10 @@
         <v>19.341756</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>33.101294</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>80.56348199999999</v>
       </c>
     </row>
     <row r="37">
@@ -1513,10 +1513,10 @@
         <v>0.27071</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>34.207806</v>
+        <v>1.106512</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>84.424324</v>
+        <v>3.860842</v>
       </c>
     </row>
     <row r="49">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.087696</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.067423</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.064996</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.06573900000000001</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.083671</v>
       </c>
     </row>
     <row r="125">
@@ -3203,19 +3203,19 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.087696</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.067423</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.064996</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.06573900000000001</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.083671</v>
       </c>
     </row>
     <row r="126">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6654,7 +6654,11 @@
           <t>Lease payments (Note 9)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -8279,7 +8283,11 @@
           <t>Lease payments (Note 9)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -9870,7 +9878,11 @@
           <t>Lease payments (Note 12)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E159" s="5" t="n">
         <v>-0.087696</v>
       </c>
@@ -10278,7 +10290,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
@@ -10315,7 +10327,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
@@ -10352,7 +10364,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -11655,7 +11667,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -13271,7 +13283,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E244" s="5" t="n">

--- a/output/pdf_financials_xlsx/EPRX.xlsx
+++ b/output/pdf_financials_xlsx/EPRX.xlsx
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.056278</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.147894</v>
+        <v>0.049485</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.155527</v>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-24.403617</v>
+        <v>-24.347339</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-19.274669</v>
+        <v>-19.373078</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-29.673448</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.056278</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.049485</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -8900,7 +8900,11 @@
           <t>Depreciation of right-of-use asset (Note 7)</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E135" s="5" t="n">
         <v>0.056278</v>
       </c>

--- a/output/pdf_financials_xlsx/EPRX.xlsx
+++ b/output/pdf_financials_xlsx/EPRX.xlsx
@@ -2895,19 +2895,19 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.431673</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.23555</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.073377</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.104227</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.588947</v>
       </c>
     </row>
     <row r="112">
@@ -3411,19 +3411,19 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.431673</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.23555</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.073377</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.104227</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.588947</v>
       </c>
     </row>
     <row r="135">
@@ -3433,19 +3433,19 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-14.826946</v>
+        <v>-15.258619</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-14.395201</v>
+        <v>-14.630751</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-20.748619</v>
+        <v>-20.821996</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-29.994491</v>
+        <v>-30.098718</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-28.552218</v>
+        <v>-29.141165</v>
       </c>
     </row>
   </sheetData>
@@ -6925,7 +6925,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -9394,7 +9398,11 @@
           <t>Acquisition of equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E147" s="5" t="n">
         <v>-0.431673</v>
       </c>
